--- a/img/RAUI.xlsx
+++ b/img/RAUI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\q32468\Desktop\RAUI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E59617D-1306-4A90-95ED-1701931CC917}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8B7532D-468A-463B-9BB7-158BD4F94D2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="READ ME" sheetId="1" r:id="rId1"/>
@@ -1150,20 +1150,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1454,40 +1453,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:3" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="5" t="s">
         <v>344</v>
       </c>
-      <c r="C1" s="4"/>
+      <c r="C1" s="5"/>
     </row>
     <row r="2" spans="2:3" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="3" t="s">
         <v>342</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="3" t="s">
         <v>343</v>
       </c>
     </row>
     <row r="3" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="4" t="s">
         <v>338</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="4" t="s">
         <v>339</v>
       </c>
     </row>
     <row r="4" spans="2:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="3" t="s">
         <v>341</v>
       </c>
     </row>
     <row r="5" spans="2:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="3" t="s">
         <v>340</v>
       </c>
     </row>
@@ -13492,37 +13491,37 @@
         <v>314</v>
       </c>
       <c r="B316" s="1">
-        <v>2.505513608372814</v>
+        <v>2.4928844698379669</v>
       </c>
       <c r="C316" s="1">
-        <v>2.0673641084750507</v>
+        <v>2.0296733962639446</v>
       </c>
       <c r="D316" s="1">
-        <v>1.6914853126002671</v>
+        <v>1.6434688040829128</v>
       </c>
       <c r="E316" s="1">
-        <v>0.6204166169305555</v>
+        <v>0.61817446576707946</v>
       </c>
       <c r="F316" s="1">
-        <v>5.7418743322215482</v>
+        <v>5.6807376862944006</v>
       </c>
       <c r="G316" s="1">
-        <v>1.9102507771681725</v>
+        <v>1.9150875999907273</v>
       </c>
       <c r="H316" s="1">
-        <v>-0.87205776421930725</v>
+        <v>-0.86774337685254976</v>
       </c>
       <c r="I316" s="1">
-        <v>1.7951647192070385E-2</v>
+        <v>-7.5713731946444648E-3</v>
       </c>
       <c r="J316" s="1">
-        <v>0.38365905828488983</v>
+        <v>0.34566515070398474</v>
       </c>
       <c r="K316" s="1">
-        <v>0.24541931428321995</v>
+        <v>0.23605003473080274</v>
       </c>
       <c r="L316" s="1">
-        <v>2.1070897755743756</v>
+        <v>2.0748955352374496</v>
       </c>
     </row>
     <row r="317" spans="1:12" x14ac:dyDescent="0.25">
@@ -13690,41 +13689,41 @@
     <col min="12" max="12" width="14.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
         <v>324</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" t="s">
         <v>325</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" t="s">
         <v>326</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" t="s">
         <v>327</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" t="s">
         <v>328</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" t="s">
         <v>329</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" t="s">
         <v>330</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" t="s">
         <v>331</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" t="s">
         <v>332</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" t="s">
         <v>333</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" t="s">
         <v>334</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" t="s">
         <v>335</v>
       </c>
     </row>
@@ -29098,47 +29097,47 @@
       </c>
       <c r="B316" s="1">
         <f>AVERAGE('RAUI-m'!B314:B316)</f>
-        <v>1.6373417993134438</v>
+        <v>1.6331320864684951</v>
       </c>
       <c r="C316" s="1">
         <f>AVERAGE('RAUI-m'!C314:C316)</f>
-        <v>2.2459157517117245</v>
+        <v>2.2333521809746895</v>
       </c>
       <c r="D316" s="1">
         <f>AVERAGE('RAUI-m'!D314:D316)</f>
-        <v>0.7514988481934971</v>
+        <v>0.73549334535437916</v>
       </c>
       <c r="E316" s="1">
         <f>AVERAGE('RAUI-m'!E314:E316)</f>
-        <v>-0.105146121243109</v>
+        <v>-0.10589350496426768</v>
       </c>
       <c r="F316" s="1">
         <f>AVERAGE('RAUI-m'!F314:F316)</f>
-        <v>1.6927080946622881</v>
+        <v>1.6723292126865721</v>
       </c>
       <c r="G316" s="1">
         <f>AVERAGE('RAUI-m'!G314:G316)</f>
-        <v>0.2662698398858403</v>
+        <v>0.26788211416002522</v>
       </c>
       <c r="H316" s="1">
         <f>AVERAGE('RAUI-m'!H314:H316)</f>
-        <v>-1.1109864058762204</v>
+        <v>-1.1095482767539682</v>
       </c>
       <c r="I316" s="1">
         <f>AVERAGE('RAUI-m'!I314:I316)</f>
-        <v>0.11710391165186339</v>
+        <v>0.1085962381896251</v>
       </c>
       <c r="J316" s="1">
         <f>AVERAGE('RAUI-m'!J314:J316)</f>
-        <v>0.12156571810318828</v>
+        <v>0.10890108224288658</v>
       </c>
       <c r="K316" s="1">
         <f>AVERAGE('RAUI-m'!K314:K316)</f>
-        <v>-0.12383344476408882</v>
+        <v>-0.12695653794822789</v>
       </c>
       <c r="L316" s="1">
         <f>AVERAGE('RAUI-m'!L314:L316)</f>
-        <v>0.80483669625916354</v>
+        <v>0.79410528281352155</v>
       </c>
     </row>
     <row r="317" spans="1:12" x14ac:dyDescent="0.25">

--- a/img/RAUI.xlsx
+++ b/img/RAUI.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\q32468\Desktop\RAUI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8B7532D-468A-463B-9BB7-158BD4F94D2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E26EE15-D994-46B3-8C6A-CCB853FC0FFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="READ ME" sheetId="1" r:id="rId1"/>
@@ -13528,17 +13528,39 @@
       <c r="A317" t="s">
         <v>315</v>
       </c>
-      <c r="B317" s="1"/>
-      <c r="C317" s="1"/>
-      <c r="D317" s="1"/>
-      <c r="E317" s="1"/>
-      <c r="F317" s="1"/>
-      <c r="G317" s="1"/>
-      <c r="H317" s="1"/>
-      <c r="I317" s="1"/>
-      <c r="J317" s="1"/>
-      <c r="K317" s="1"/>
-      <c r="L317" s="1"/>
+      <c r="B317" s="1">
+        <v>1.4500078558794194</v>
+      </c>
+      <c r="C317" s="1">
+        <v>1.5769495381724599</v>
+      </c>
+      <c r="D317" s="1">
+        <v>1.0739145465949751</v>
+      </c>
+      <c r="E317" s="1">
+        <v>0.12337114236574065</v>
+      </c>
+      <c r="F317" s="1">
+        <v>3.6175018467157383</v>
+      </c>
+      <c r="G317" s="1">
+        <v>1.4388688244491581</v>
+      </c>
+      <c r="H317" s="1">
+        <v>0.12891024983334518</v>
+      </c>
+      <c r="I317" s="1">
+        <v>-0.10915244720178274</v>
+      </c>
+      <c r="J317" s="1">
+        <v>0.70035566948025307</v>
+      </c>
+      <c r="K317" s="1">
+        <v>0.42884980689138852</v>
+      </c>
+      <c r="L317" s="1">
+        <v>1.519687941758874</v>
+      </c>
     </row>
     <row r="318" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
